--- a/output/pdf_financials_xlsx/ABX.xlsx
+++ b/output/pdf_financials_xlsx/ABX.xlsx
@@ -5811,22 +5811,22 @@
         <v>0</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-28</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-26</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="125">
@@ -5854,22 +5854,22 @@
         <v>0</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-28</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-26</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="126">
@@ -23464,7 +23464,11 @@
           <t>Lease repayments</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -25884,7 +25888,11 @@
           <t>Lease repayments</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ABX.xlsx
+++ b/output/pdf_financials_xlsx/ABX.xlsx
@@ -1097,7 +1097,7 @@
         <v>630</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1868</v>
+        <v>306</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-31</v>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-10603</v>
+        <v>-10097</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-2959</v>
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-506</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>-6.654695257209253</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-70.41085563513005</v>
+        <v>-11.53411232566905</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0.9860050890585241</v>
@@ -2191,16 +2191,16 @@
         <v>0</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>366</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>447</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
     </row>
     <row r="41">
@@ -2234,16 +2234,16 @@
         <v>558</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>554</v>
+        <v>935</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>623</v>
+        <v>989</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0</v>
+        <v>447</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>693</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="42">
@@ -2541,7 +2541,7 @@
         <v>612</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>3290</v>
+        <v>2843</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>815</v>
@@ -2897,22 +2897,22 @@
         <v>0</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>61862</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>63793</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>64937</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0</v>
+        <v>68542</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0</v>
+        <v>70856</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0</v>
+        <v>73961</v>
       </c>
     </row>
     <row r="57">
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>-10603</v>
+        <v>-10097</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-2959</v>
@@ -5105,13 +5105,13 @@
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>0</v>
+        <v>12687</v>
       </c>
       <c r="C108" s="3" t="n">
-        <v>0</v>
+        <v>4106</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>0</v>
+        <v>3897</v>
       </c>
       <c r="E108" s="3" t="n">
         <v>0</v>
@@ -5132,10 +5132,10 @@
         <v>0</v>
       </c>
       <c r="K108" s="3" t="n">
-        <v>0</v>
+        <v>1671</v>
       </c>
       <c r="L108" s="3" t="n">
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="M108" s="3" t="n">
         <v>0</v>
@@ -24372,7 +24372,11 @@
           <t>Net impairment charges (notes 10 and 21)</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -25312,7 +25316,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E265" t="inlineStr">
         <is>
           <t>-</t>
@@ -28974,7 +28982,11 @@
           <t>Impairment charges (note 9b)</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E315" s="5" t="n">
         <v>12687</v>
       </c>
@@ -30388,7 +30400,11 @@
           <t>Net loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E334" s="5" t="n">
         <v>-10097</v>
       </c>
@@ -39278,7 +39294,11 @@
           <t>Income tax recovery (expense) (note 11)</t>
         </is>
       </c>
-      <c r="D456" t="inlineStr"/>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E456" t="inlineStr">
         <is>
           <t>-</t>
@@ -39800,7 +39820,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D463" t="inlineStr"/>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E463" s="5" t="n">
         <v>-10097</v>
       </c>
@@ -39874,7 +39898,11 @@
           <t>Loss from discontinued operations (note 4e)</t>
         </is>
       </c>
-      <c r="D464" t="inlineStr"/>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E464" s="5" t="n">
         <v>-506</v>
       </c>
